--- a/Valuation Framework.xlsx
+++ b/Valuation Framework.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64AF688-204F-4865-BE2B-D255918DF152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3170006-6170-47DB-ADE9-188AC10D6FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="4" xr2:uid="{E998409C-6030-4F13-BFA3-5FA46D863087}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E998409C-6030-4F13-BFA3-5FA46D863087}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="WACC">DCF!$E$18</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1258,6 +1258,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1275,9 +1278,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -21799,7 +21799,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="K2" s="86" t="s">
+      <c r="K2" s="80" t="s">
         <v>206</v>
       </c>
       <c r="L2" s="3"/>
@@ -27934,7 +27934,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="29">
         <f ca="1">+TODAY()</f>
-        <v>46237</v>
+        <v>46262</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
@@ -30851,43 +30851,43 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>126.59166666666667</v>
+        <v>126.66111111111111</v>
       </c>
       <c r="N53" s="3">
         <f ca="1">M53+1</f>
-        <v>127.59166666666667</v>
+        <v>127.66111111111111</v>
       </c>
       <c r="O53" s="3">
         <f ca="1">N53+1</f>
-        <v>128.59166666666667</v>
+        <v>128.6611111111111</v>
       </c>
       <c r="P53" s="3">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>129.59166666666667</v>
+        <v>129.6611111111111</v>
       </c>
       <c r="Q53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>130.59166666666667</v>
+        <v>130.6611111111111</v>
       </c>
       <c r="R53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>131.59166666666667</v>
+        <v>131.6611111111111</v>
       </c>
       <c r="S53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>132.59166666666667</v>
+        <v>132.6611111111111</v>
       </c>
       <c r="T53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>133.59166666666667</v>
+        <v>133.6611111111111</v>
       </c>
       <c r="U53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>134.59166666666667</v>
+        <v>134.6611111111111</v>
       </c>
       <c r="V53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>135.59166666666667</v>
+        <v>135.6611111111111</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
@@ -31586,29 +31586,29 @@
     <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="63"/>
-      <c r="C68" s="80" t="s">
+      <c r="C68" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="D68" s="80"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="80"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="80"/>
-      <c r="I68" s="80"/>
-      <c r="J68" s="81"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81"/>
+      <c r="J68" s="82"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="63"/>
-      <c r="N68" s="82" t="s">
+      <c r="N68" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="O68" s="82"/>
-      <c r="P68" s="82"/>
-      <c r="Q68" s="82"/>
-      <c r="R68" s="82"/>
-      <c r="S68" s="82"/>
-      <c r="T68" s="82"/>
-      <c r="U68" s="83"/>
+      <c r="O68" s="83"/>
+      <c r="P68" s="83"/>
+      <c r="Q68" s="83"/>
+      <c r="R68" s="83"/>
+      <c r="S68" s="83"/>
+      <c r="T68" s="83"/>
+      <c r="U68" s="84"/>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
@@ -31634,7 +31634,7 @@
     </row>
     <row r="69" spans="1:43" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
-      <c r="B69" s="84" t="s">
+      <c r="B69" s="85" t="s">
         <v>29</v>
       </c>
       <c r="C69" s="64" t="e">
@@ -31650,7 +31650,7 @@
       <c r="J69" s="65"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
-      <c r="M69" s="84" t="s">
+      <c r="M69" s="85" t="s">
         <v>29</v>
       </c>
       <c r="N69" s="64" t="e">
@@ -31689,7 +31689,7 @@
     </row>
     <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="84"/>
+      <c r="B70" s="85"/>
       <c r="C70" s="66"/>
       <c r="D70" s="67"/>
       <c r="E70" s="67"/>
@@ -31700,7 +31700,7 @@
       <c r="J70" s="67"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
-      <c r="M70" s="84"/>
+      <c r="M70" s="85"/>
       <c r="N70" s="66"/>
       <c r="O70" s="67"/>
       <c r="P70" s="67"/>
@@ -31734,7 +31734,7 @@
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="84"/>
+      <c r="B71" s="85"/>
       <c r="C71" s="66"/>
       <c r="D71" s="67"/>
       <c r="E71" s="67"/>
@@ -31745,7 +31745,7 @@
       <c r="J71" s="67"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="84"/>
+      <c r="M71" s="85"/>
       <c r="N71" s="66"/>
       <c r="O71" s="67"/>
       <c r="P71" s="67"/>
@@ -31779,7 +31779,7 @@
     </row>
     <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
-      <c r="B72" s="84"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="66"/>
       <c r="D72" s="68"/>
       <c r="E72" s="68"/>
@@ -31790,7 +31790,7 @@
       <c r="J72" s="68"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="84"/>
+      <c r="M72" s="85"/>
       <c r="N72" s="66"/>
       <c r="O72" s="68"/>
       <c r="P72" s="68"/>
@@ -31824,7 +31824,7 @@
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="B73" s="84"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="66"/>
       <c r="D73" s="67"/>
       <c r="E73" s="67"/>
@@ -31835,7 +31835,7 @@
       <c r="J73" s="67"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="84"/>
+      <c r="M73" s="85"/>
       <c r="N73" s="66"/>
       <c r="O73" s="67"/>
       <c r="P73" s="67"/>
@@ -31869,7 +31869,7 @@
     </row>
     <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="84"/>
+      <c r="B74" s="85"/>
       <c r="C74" s="66"/>
       <c r="D74" s="67"/>
       <c r="E74" s="67"/>
@@ -31880,7 +31880,7 @@
       <c r="J74" s="67"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
-      <c r="M74" s="84"/>
+      <c r="M74" s="85"/>
       <c r="N74" s="66"/>
       <c r="O74" s="67"/>
       <c r="P74" s="67"/>
@@ -31914,7 +31914,7 @@
     </row>
     <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
-      <c r="B75" s="84"/>
+      <c r="B75" s="85"/>
       <c r="C75" s="66"/>
       <c r="D75" s="67"/>
       <c r="E75" s="67"/>
@@ -31925,7 +31925,7 @@
       <c r="J75" s="67"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="84"/>
+      <c r="M75" s="85"/>
       <c r="N75" s="66"/>
       <c r="O75" s="67"/>
       <c r="P75" s="67"/>
@@ -31959,7 +31959,7 @@
     </row>
     <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
-      <c r="B76" s="85"/>
+      <c r="B76" s="86"/>
       <c r="C76" s="66"/>
       <c r="D76" s="67"/>
       <c r="E76" s="67"/>
@@ -31970,7 +31970,7 @@
       <c r="J76" s="67"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
-      <c r="M76" s="85"/>
+      <c r="M76" s="86"/>
       <c r="N76" s="66"/>
       <c r="O76" s="67"/>
       <c r="P76" s="67"/>
